--- a/data/trans_dic/P16A12-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,01</t>
+          <t>3,2; 7,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,71</t>
+          <t>2,74; 6,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,28</t>
+          <t>4,89; 10,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,07</t>
+          <t>5,83; 10,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,63</t>
+          <t>0,59; 3,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,58</t>
+          <t>1,92; 6,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,18</t>
+          <t>2,04; 6,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,65</t>
+          <t>2,16; 4,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,04</t>
+          <t>2,53; 5,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,98</t>
+          <t>2,81; 5,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,45</t>
+          <t>4,05; 7,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,99</t>
+          <t>4,4; 7,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,75</t>
+          <t>2,61; 6,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,36</t>
+          <t>3,54; 7,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,67</t>
+          <t>3,94; 8,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 12,2</t>
+          <t>7,13; 12,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,36</t>
+          <t>0,54; 3,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,18</t>
+          <t>1,18; 5,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,11</t>
+          <t>1,22; 5,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,78</t>
+          <t>1,47; 3,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,41</t>
+          <t>1,95; 4,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,96</t>
+          <t>2,83; 5,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,21</t>
+          <t>3,09; 6,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,62</t>
+          <t>4,82; 7,69</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,44</t>
+          <t>3,48; 7,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 12,92</t>
+          <t>8,0; 12,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 13,02</t>
+          <t>7,72; 13,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 11,67</t>
+          <t>2,27; 11,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,1</t>
+          <t>4,21; 12,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,15</t>
+          <t>3,84; 9,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,88</t>
+          <t>3,22; 11,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 13,28</t>
+          <t>6,98; 13,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,56</t>
+          <t>4,16; 7,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,64</t>
+          <t>7,32; 11,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,72</t>
+          <t>7,12; 11,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,28</t>
+          <t>3,43; 11,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,06</t>
+          <t>6,1; 9,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,8</t>
+          <t>7,23; 10,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,99</t>
+          <t>7,53; 10,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 12,33</t>
+          <t>8,98; 12,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,07</t>
+          <t>3,05; 5,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,86</t>
+          <t>3,52; 6,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,29</t>
+          <t>2,56; 5,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,7</t>
+          <t>2,03; 5,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,45</t>
+          <t>5,28; 7,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,7</t>
+          <t>6,26; 8,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 8,1</t>
+          <t>5,83; 8,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,87</t>
+          <t>4,95; 8,84</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 9,28</t>
+          <t>4,02; 9,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,27</t>
+          <t>4,85; 9,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,41</t>
+          <t>8,54; 13,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 11,53</t>
+          <t>6,76; 11,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,53</t>
+          <t>3,49; 7,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,9; 10,92</t>
+          <t>7,0; 11,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 11,89</t>
+          <t>7,15; 11,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,1</t>
+          <t>7,45; 11,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,39</t>
+          <t>4,34; 7,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,84</t>
+          <t>6,77; 9,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,32; 11,69</t>
+          <t>8,47; 11,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,09</t>
+          <t>7,8; 11,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,05</t>
+          <t>0,72; 5,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,43</t>
+          <t>0,4; 3,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,78</t>
+          <t>0,2; 2,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,47</t>
+          <t>8,22; 11,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,95; 15,98</t>
+          <t>11,97; 16,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,4; 15,7</t>
+          <t>11,36; 15,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,34; 12,9</t>
+          <t>9,51; 12,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,59; 9,49</t>
+          <t>6,7; 9,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,45</t>
+          <t>9,96; 13,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,14; 12,57</t>
+          <t>9,22; 12,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,96</t>
+          <t>7,3; 10,11</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 6,48</t>
+          <t>4,83; 6,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,33</t>
+          <t>6,47; 8,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,56; 9,45</t>
+          <t>7,43; 9,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,39</t>
+          <t>6,4; 9,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,93</t>
+          <t>5,28; 6,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,35</t>
+          <t>7,57; 9,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 8,91</t>
+          <t>6,97; 8,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,78</t>
+          <t>5,71; 7,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,4</t>
+          <t>5,28; 6,38</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,61</t>
+          <t>7,24; 8,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,83</t>
+          <t>7,49; 8,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,35</t>
+          <t>6,53; 8,35</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14712; 33227</t>
+          <t>15184; 34103</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11073; 29331</t>
+          <t>11974; 29247</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21160; 44129</t>
+          <t>20992; 45116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29450; 50874</t>
+          <t>29462; 51844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1828; 11129</t>
+          <t>1805; 11534</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6061; 20697</t>
+          <t>6032; 21717</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7093; 21432</t>
+          <t>7066; 21625</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9447; 20786</t>
+          <t>9660; 20069</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18495; 39364</t>
+          <t>19708; 41343</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21578; 44936</t>
+          <t>21123; 45047</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31538; 57818</t>
+          <t>31469; 57893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41950; 66600</t>
+          <t>41950; 66679</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10118; 24772</t>
+          <t>9586; 24982</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13745; 30692</t>
+          <t>14743; 33295</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15244; 32712</t>
+          <t>14875; 33138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31986; 55176</t>
+          <t>32231; 54761</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2043; 12501</t>
+          <t>1999; 12117</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4054; 17383</t>
+          <t>3945; 17045</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4395; 19037</t>
+          <t>4546; 19978</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5787; 14468</t>
+          <t>5640; 14750</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14050; 32579</t>
+          <t>14432; 33205</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21327; 44808</t>
+          <t>21286; 44144</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22942; 46519</t>
+          <t>23196; 47470</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39861; 63622</t>
+          <t>40259; 64206</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19275; 40367</t>
+          <t>18861; 38790</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50205; 81196</t>
+          <t>50269; 81031</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39335; 67973</t>
+          <t>40282; 68118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15058; 78013</t>
+          <t>15195; 77905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6844; 20306</t>
+          <t>7070; 20834</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9431; 26181</t>
+          <t>9892; 25669</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5280; 19738</t>
+          <t>5349; 19466</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11227; 22165</t>
+          <t>11646; 22799</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29862; 53660</t>
+          <t>29529; 53853</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65840; 103163</t>
+          <t>64875; 99892</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48811; 80616</t>
+          <t>49009; 78835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25555; 94224</t>
+          <t>28656; 93428</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74604; 112200</t>
+          <t>75512; 111991</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84606; 125030</t>
+          <t>83632; 124449</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86722; 126307</t>
+          <t>86523; 124797</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91316; 127614</t>
+          <t>92940; 127632</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21591; 43363</t>
+          <t>21754; 42760</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27609; 52563</t>
+          <t>26969; 52818</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20178; 43678</t>
+          <t>21151; 44226</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21161; 55701</t>
+          <t>19859; 57060</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>104212; 145386</t>
+          <t>103094; 145490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120775; 167462</t>
+          <t>120496; 169882</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116115; 159929</t>
+          <t>115077; 162414</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>105563; 178472</t>
+          <t>99656; 177887</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14251; 32438</t>
+          <t>14039; 32827</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24343; 47343</t>
+          <t>24747; 48846</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52585; 83246</t>
+          <t>52988; 82422</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32211; 54662</t>
+          <t>32057; 54881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19870; 42818</t>
+          <t>19871; 41092</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52390; 82898</t>
+          <t>53183; 85054</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53317; 87746</t>
+          <t>52750; 85261</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>62020; 101559</t>
+          <t>62532; 99744</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38134; 67899</t>
+          <t>39858; 66681</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84740; 124935</t>
+          <t>86022; 124842</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113002; 158925</t>
+          <t>115088; 158530</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>102296; 145619</t>
+          <t>102456; 145808</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4587</t>
+          <t>0; 4614</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1939; 13432</t>
+          <t>1912; 13310</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1077; 9850</t>
+          <t>1136; 10765</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>482; 6694</t>
+          <t>481; 6077</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>101145; 143211</t>
+          <t>102654; 143851</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>132029; 176609</t>
+          <t>132334; 180203</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>123379; 169825</t>
+          <t>122888; 171396</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>70992; 98045</t>
+          <t>72255; 98738</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102013; 146871</t>
+          <t>103680; 145598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135291; 184467</t>
+          <t>136576; 186079</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>125150; 172038</t>
+          <t>126185; 176570</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>72805; 99691</t>
+          <t>73005; 101203</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>159449; 211810</t>
+          <t>157786; 208829</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>222650; 284519</t>
+          <t>221121; 283928</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>255846; 319842</t>
+          <t>251519; 312737</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>209292; 316822</t>
+          <t>216062; 317026</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>179170; 234233</t>
+          <t>178419; 231603</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>264424; 330724</t>
+          <t>267849; 335566</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>241726; 314529</t>
+          <t>246107; 309954</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>201652; 278113</t>
+          <t>203934; 277490</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>350504; 425708</t>
+          <t>351079; 424306</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>499680; 599141</t>
+          <t>503899; 599083</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>516352; 610851</t>
+          <t>517966; 612515</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>461581; 580447</t>
+          <t>454049; 579874</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A12-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A12-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,2</t>
+          <t>3,05; 7,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,69</t>
+          <t>2,54; 6,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,51</t>
+          <t>4,87; 10,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,26</t>
+          <t>5,94; 10,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,76</t>
+          <t>0,59; 3,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,91</t>
+          <t>1,91; 6,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,23</t>
+          <t>1,85; 6,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,49</t>
+          <t>2,06; 4,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,3</t>
+          <t>2,37; 5,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,99</t>
+          <t>2,82; 6,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,46</t>
+          <t>4,12; 7,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,0</t>
+          <t>4,33; 6,69</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,81</t>
+          <t>2,75; 6,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,98</t>
+          <t>3,36; 7,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,78</t>
+          <t>4,07; 8,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,11</t>
+          <t>6,49; 11,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,26</t>
+          <t>0,52; 3,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,08</t>
+          <t>1,23; 5,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,37</t>
+          <t>1,19; 5,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,86</t>
+          <t>1,56; 3,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,49</t>
+          <t>1,97; 4,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,87</t>
+          <t>2,77; 5,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,33</t>
+          <t>3,01; 6,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,69</t>
+          <t>4,63; 7,38</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,15</t>
+          <t>3,65; 7,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 12,9</t>
+          <t>8,11; 13,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,05</t>
+          <t>7,42; 13,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 11,66</t>
+          <t>7,94; 12,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,42</t>
+          <t>4,2; 12,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,95</t>
+          <t>3,67; 10,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 11,72</t>
+          <t>3,1; 11,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 13,66</t>
+          <t>6,9; 13,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,58</t>
+          <t>4,17; 7,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 11,27</t>
+          <t>7,2; 11,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 11,46</t>
+          <t>7,42; 11,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 11,19</t>
+          <t>8,39; 12,48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,04</t>
+          <t>6,07; 9,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,75</t>
+          <t>7,19; 10,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 10,86</t>
+          <t>7,87; 11,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,33</t>
+          <t>9,2; 12,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,99</t>
+          <t>3,01; 5,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,89</t>
+          <t>3,7; 7,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,36</t>
+          <t>2,46; 5,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,84</t>
+          <t>4,23; 6,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,45</t>
+          <t>5,23; 7,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 8,83</t>
+          <t>6,27; 8,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,22</t>
+          <t>5,79; 8,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,84</t>
+          <t>7,27; 9,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,39</t>
+          <t>4,07; 9,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,57</t>
+          <t>4,71; 9,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 13,28</t>
+          <t>8,43; 13,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,58</t>
+          <t>6,18; 10,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,22</t>
+          <t>3,45; 7,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,2</t>
+          <t>6,79; 11,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,55</t>
+          <t>7,05; 11,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,89</t>
+          <t>9,37; 12,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,26</t>
+          <t>4,3; 7,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 9,83</t>
+          <t>6,61; 9,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,67</t>
+          <t>8,32; 11,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 11,1</t>
+          <t>8,65; 11,1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,01</t>
+          <t>0,74; 5,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,75</t>
+          <t>0,39; 3,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,53</t>
+          <t>0,23; 2,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,52</t>
+          <t>8,3; 11,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,3</t>
+          <t>12,11; 16,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,84</t>
+          <t>11,26; 15,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,51; 12,99</t>
+          <t>9,2; 12,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,41</t>
+          <t>6,77; 9,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 13,57</t>
+          <t>9,97; 13,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,22; 12,9</t>
+          <t>9,07; 12,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,11</t>
+          <t>7,35; 10,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 6,39</t>
+          <t>4,82; 6,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,31</t>
+          <t>6,44; 8,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,24</t>
+          <t>7,53; 9,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,39</t>
+          <t>8,04; 9,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,86</t>
+          <t>5,33; 6,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 9,48</t>
+          <t>7,61; 9,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,78</t>
+          <t>7,03; 8,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 7,76</t>
+          <t>6,78; 8,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,38</t>
+          <t>5,28; 6,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,61</t>
+          <t>7,21; 8,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,49; 8,85</t>
+          <t>7,51; 8,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,35</t>
+          <t>7,6; 8,7</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>42131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>57120</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15184; 34103</t>
+          <t>14427; 33428</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11974; 29247</t>
+          <t>11087; 29395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20992; 45116</t>
+          <t>20893; 44527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29462; 51844</t>
+          <t>32723; 55888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1805; 11534</t>
+          <t>1795; 11136</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6032; 21717</t>
+          <t>6020; 21006</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7066; 21625</t>
+          <t>6428; 21174</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9660; 20069</t>
+          <t>10040; 21453</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19708; 41343</t>
+          <t>18511; 39145</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21123; 45047</t>
+          <t>21191; 46638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31469; 57893</t>
+          <t>31959; 59385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41950; 66679</t>
+          <t>45005; 69546</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41878</t>
+          <t>42981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51096</t>
+          <t>53698</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9586; 24982</t>
+          <t>10090; 25532</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14743; 33295</t>
+          <t>14006; 32501</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14875; 33138</t>
+          <t>15345; 33507</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32231; 54761</t>
+          <t>31337; 55352</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1999; 12117</t>
+          <t>1923; 12598</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3945; 17045</t>
+          <t>4122; 17395</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4546; 19978</t>
+          <t>4417; 19613</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5640; 14750</t>
+          <t>6593; 16443</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14432; 33205</t>
+          <t>14527; 30943</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21286; 44144</t>
+          <t>20836; 43309</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23196; 47470</t>
+          <t>22593; 45649</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40259; 64206</t>
+          <t>41985; 66864</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62732</t>
+          <t>66960</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18861; 38790</t>
+          <t>19789; 38846</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50269; 81031</t>
+          <t>50950; 82760</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40282; 68118</t>
+          <t>38751; 68331</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15195; 77905</t>
+          <t>37439; 60390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7070; 20834</t>
+          <t>7039; 21206</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9892; 25669</t>
+          <t>9455; 26382</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5349; 19466</t>
+          <t>5151; 19908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11646; 22799</t>
+          <t>12942; 24779</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29529; 53853</t>
+          <t>29591; 55337</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64875; 99892</t>
+          <t>63781; 101204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49009; 78835</t>
+          <t>51022; 81718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28656; 93428</t>
+          <t>55329; 82269</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108667</t>
+          <t>121562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>44883</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>149975</t>
+          <t>166445</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75512; 111991</t>
+          <t>75147; 111639</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83632; 124449</t>
+          <t>83216; 124801</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86523; 124797</t>
+          <t>90438; 128692</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92940; 127632</t>
+          <t>104181; 141625</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21754; 42760</t>
+          <t>21479; 42352</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26969; 52818</t>
+          <t>28328; 55543</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21151; 44226</t>
+          <t>20306; 43682</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19859; 57060</t>
+          <t>36382; 55005</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103094; 145490</t>
+          <t>102174; 143552</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120496; 169882</t>
+          <t>120712; 168675</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>115077; 162414</t>
+          <t>114419; 160879</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>99656; 177887</t>
+          <t>144762; 189444</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>46299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84229</t>
+          <t>91382</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>126410</t>
+          <t>137680</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14039; 32827</t>
+          <t>14225; 33089</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24747; 48846</t>
+          <t>24055; 48427</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52988; 82422</t>
+          <t>52343; 82260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32057; 54881</t>
+          <t>35051; 58847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19871; 41092</t>
+          <t>19644; 42368</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53183; 85054</t>
+          <t>51564; 83929</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52750; 85261</t>
+          <t>52036; 85347</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>62532; 99744</t>
+          <t>77821; 105592</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39858; 66681</t>
+          <t>39499; 68143</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86022; 124842</t>
+          <t>83915; 122595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>115088; 158530</t>
+          <t>113129; 159770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>102456; 145808</t>
+          <t>120876; 155015</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>84369</t>
+          <t>91483</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86390</t>
+          <t>93497</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>0; 4599</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1912; 13310</t>
+          <t>1965; 14014</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1136; 10765</t>
+          <t>1122; 9398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>481; 6077</t>
+          <t>536; 6006</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>102654; 143851</t>
+          <t>103620; 142769</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>132334; 180203</t>
+          <t>133795; 179596</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>122888; 171396</t>
+          <t>121800; 168151</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>72255; 98738</t>
+          <t>77558; 105820</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>103680; 145598</t>
+          <t>104714; 147323</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136576; 186079</t>
+          <t>136644; 185291</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126185; 176570</t>
+          <t>124172; 174375</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73005; 101203</t>
+          <t>79403; 109036</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>280177</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>249577</t>
+          <t>271830</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>529754</t>
+          <t>575399</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>157786; 208829</t>
+          <t>157677; 207883</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>221121; 283928</t>
+          <t>220119; 290195</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>251519; 312737</t>
+          <t>254791; 316682</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>216062; 317026</t>
+          <t>276570; 335875</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>178419; 231603</t>
+          <t>179925; 234873</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>267849; 335566</t>
+          <t>269439; 333320</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>246107; 309954</t>
+          <t>248411; 314310</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>203934; 277490</t>
+          <t>246156; 296531</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>351079; 424306</t>
+          <t>351243; 428348</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>503899; 599083</t>
+          <t>501314; 598584</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>517966; 612515</t>
+          <t>519245; 612017</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>454049; 579874</t>
+          <t>537713; 615713</t>
         </is>
       </c>
     </row>
